--- a/client/public/import-templates/reisekosten-import-testdaten-v1.xlsx
+++ b/client/public/import-templates/reisekosten-import-testdaten-v1.xlsx
@@ -595,7 +595,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:AC6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -635,45 +635,54 @@
         <v>flight_route_type</v>
       </c>
       <c r="M1" t="str">
+        <v>departure_airport</v>
+      </c>
+      <c r="N1" t="str">
+        <v>arrival_airport</v>
+      </c>
+      <c r="O1" t="str">
+        <v>flight_direction</v>
+      </c>
+      <c r="P1" t="str">
         <v>departure_time</v>
       </c>
-      <c r="N1" t="str">
+      <c r="Q1" t="str">
         <v>arrival_time</v>
       </c>
-      <c r="O1" t="str">
+      <c r="R1" t="str">
         <v>return_date</v>
       </c>
-      <c r="P1" t="str">
+      <c r="S1" t="str">
         <v>ticket_number</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="T1" t="str">
         <v>flight_number</v>
       </c>
-      <c r="R1" t="str">
+      <c r="U1" t="str">
         <v>check_in_date</v>
       </c>
-      <c r="S1" t="str">
+      <c r="V1" t="str">
         <v>check_out_date</v>
       </c>
-      <c r="T1" t="str">
+      <c r="W1" t="str">
         <v>nights</v>
       </c>
-      <c r="U1" t="str">
+      <c r="X1" t="str">
         <v>distance_km</v>
       </c>
-      <c r="V1" t="str">
+      <c r="Y1" t="str">
         <v>rate_per_km</v>
       </c>
-      <c r="W1" t="str">
+      <c r="Z1" t="str">
         <v>liters</v>
       </c>
-      <c r="X1" t="str">
+      <c r="AA1" t="str">
         <v>price_per_liter</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AB1" t="str">
         <v>receipt_no</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AC1" t="str">
         <v>vendor_name</v>
       </c>
     </row>
@@ -751,9 +760,18 @@
         <v/>
       </c>
       <c r="Y2" t="str">
+        <v/>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v/>
+      </c>
+      <c r="AB2" t="str">
         <v>TX-88421</v>
       </c>
-      <c r="Z2" t="str">
+      <c r="AC2" t="str">
         <v>iTaxi</v>
       </c>
     </row>
@@ -792,32 +810,32 @@
         <v>Hinflug MUC-WAW</v>
       </c>
       <c r="L3" t="str">
-        <v>domestic</v>
+        <v>international</v>
       </c>
       <c r="M3" t="str">
+        <v>MUC</v>
+      </c>
+      <c r="N3" t="str">
+        <v>WAW</v>
+      </c>
+      <c r="O3" t="str">
+        <v>outbound</v>
+      </c>
+      <c r="P3" t="str">
         <v>08:30</v>
       </c>
-      <c r="N3" t="str">
+      <c r="Q3" t="str">
         <v>10:05</v>
       </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
         <v>LH2040</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="T3" t="str">
         <v>LH2040</v>
       </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
-        <v/>
-      </c>
       <c r="U3" t="str">
         <v/>
       </c>
@@ -831,9 +849,18 @@
         <v/>
       </c>
       <c r="Y3" t="str">
+        <v/>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v/>
+      </c>
+      <c r="AB3" t="str">
         <v>FL-2201</v>
       </c>
-      <c r="Z3" t="str">
+      <c r="AC3" t="str">
         <v>Lufthansa</v>
       </c>
     </row>
@@ -890,30 +917,39 @@
         <v/>
       </c>
       <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str">
         <v>2026-03-03</v>
       </c>
-      <c r="S4" t="str">
+      <c r="V4" t="str">
         <v>2026-03-06</v>
       </c>
-      <c r="T4">
+      <c r="W4">
         <v>3</v>
       </c>
-      <c r="U4" t="str">
-        <v/>
-      </c>
-      <c r="V4" t="str">
-        <v/>
-      </c>
-      <c r="W4" t="str">
-        <v/>
-      </c>
       <c r="X4" t="str">
         <v/>
       </c>
       <c r="Y4" t="str">
+        <v/>
+      </c>
+      <c r="Z4" t="str">
+        <v/>
+      </c>
+      <c r="AA4" t="str">
+        <v/>
+      </c>
+      <c r="AB4" t="str">
         <v>HT-7712</v>
       </c>
-      <c r="Z4" t="str">
+      <c r="AC4" t="str">
         <v>Hotel Centrum</v>
       </c>
     </row>
@@ -984,16 +1020,25 @@
       <c r="V5" t="str">
         <v/>
       </c>
-      <c r="W5">
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5">
         <v>42.3</v>
       </c>
-      <c r="X5">
+      <c r="AA5">
         <v>7.58</v>
       </c>
-      <c r="Y5" t="str">
+      <c r="AB5" t="str">
         <v>FU-1190</v>
       </c>
-      <c r="Z5" t="str">
+      <c r="AC5" t="str">
         <v>Orlen</v>
       </c>
     </row>
@@ -1071,15 +1116,24 @@
         <v/>
       </c>
       <c r="Y6" t="str">
+        <v/>
+      </c>
+      <c r="Z6" t="str">
+        <v/>
+      </c>
+      <c r="AA6" t="str">
+        <v/>
+      </c>
+      <c r="AB6" t="str">
         <v>ME-1102</v>
       </c>
-      <c r="Z6" t="str">
+      <c r="AC6" t="str">
         <v>Bistro WAW</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AC6"/>
   </ignoredErrors>
 </worksheet>
 </file>